--- a/artfynd/A 10364-2026 artfynd.xlsx
+++ b/artfynd/A 10364-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103797767</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519485.421146842</v>
+        <v>519485</v>
       </c>
       <c r="R2" t="n">
-        <v>7208549.781820158</v>
+        <v>7208550</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +775,11 @@
         <v>103797765</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519441.0805288265</v>
+        <v>519441</v>
       </c>
       <c r="R3" t="n">
-        <v>7208398.437278229</v>
+        <v>7208398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103797766</v>
+        <v>103797762</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519480.390430368</v>
+        <v>519381</v>
       </c>
       <c r="R4" t="n">
-        <v>7208541.709789203</v>
+        <v>7208392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +937,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,55 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103797764</v>
+        <v>103797763</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519435.1111561817</v>
+        <v>519389</v>
       </c>
       <c r="R5" t="n">
-        <v>7208404.322228508</v>
+        <v>7208381</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1034,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,16 +1066,11 @@
         <v>103797768</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1173,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519502.3846792686</v>
+        <v>519503</v>
       </c>
       <c r="R6" t="n">
-        <v>7208546.93095728</v>
+        <v>7208547</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,19 +1131,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103797763</v>
+        <v>103797764</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,34 +1171,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519389.5055458367</v>
+        <v>519435</v>
       </c>
       <c r="R7" t="n">
-        <v>7208381.599128028</v>
+        <v>7208404</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1233,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103797762</v>
+        <v>103797766</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,34 +1273,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519381.3850990884</v>
+        <v>519481</v>
       </c>
       <c r="R8" t="n">
-        <v>7208392.547850481</v>
+        <v>7208542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,19 +1335,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,12 +1367,7 @@
         <v>107892451</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
